--- a/TEMPLATES/Mitra Commission Intake - MASTER TEMPLATE.xlsx
+++ b/TEMPLATES/Mitra Commission Intake - MASTER TEMPLATE.xlsx
@@ -896,12 +896,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>New/changed Mitra master data + ownership / SKB.</t>
+          <t>One row per NEW or CHANGED Mitra — full master (DPID, DPMS, owner, region, tax/NIK/NPWP, addresses, bank, Netsuite ID, SKB, hold-comm).</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Feeds Data Sources + PPh: sets entity type (tax rate), SKB, bank details, hold-commission flag.</t>
+          <t>The single Data Sources feed: upserted into the mitra master by DPID (new DPID appended). Also feeds PPh: entity type (tax rate), SKB, bank details, hold-commission flag.</t>
         </is>
       </c>
     </row>
@@ -1228,106 +1228,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
+          <t>DPID</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
           <t>DPMS ID</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>DP Name</t>
-        </is>
-      </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
+          <t>Mitra Name</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Per Mitra Name</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
           <t>Owner Name</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Customer ID Netsuite</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Nama Owner di NS (Data DJP)</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>NIK</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>Tax ID</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>Tax ID (16 digit)</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>Jenis Usaha</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>Alamat NIK</t>
+        </is>
+      </c>
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>Alamat NPWP</t>
+        </is>
+      </c>
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>Address 1</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="Q1" s="14" t="inlineStr">
         <is>
           <t>Address 2</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="R1" s="14" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
-        <is>
-          <t>Account Holder</t>
-        </is>
-      </c>
-      <c r="L1" s="14" t="inlineStr">
-        <is>
-          <t>Account Number</t>
-        </is>
-      </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
+        <is>
+          <t>Nama Pemilik</t>
+        </is>
+      </c>
+      <c r="T1" s="14" t="inlineStr">
+        <is>
+          <t>Nomor Rekening</t>
+        </is>
+      </c>
+      <c r="U1" s="14" t="inlineStr">
+        <is>
+          <t>CUSID netsuite</t>
+        </is>
+      </c>
+      <c r="V1" s="14" t="inlineStr">
+        <is>
+          <t>Hold Commission</t>
+        </is>
+      </c>
+      <c r="W1" s="14" t="inlineStr">
+        <is>
+          <t>Note Perubahan</t>
+        </is>
+      </c>
+      <c r="X1" s="14" t="inlineStr">
+        <is>
+          <t>Drop Off to SH Remarks</t>
+        </is>
+      </c>
+      <c r="Y1" s="14" t="inlineStr">
+        <is>
+          <t>MPM/Last Mile Remarks</t>
+        </is>
+      </c>
+      <c r="Z1" s="14" t="inlineStr">
+        <is>
+          <t>PKP Remarks</t>
+        </is>
+      </c>
+      <c r="AA1" s="14" t="inlineStr">
         <is>
           <t>SKB Number</t>
         </is>
       </c>
-      <c r="N1" s="14" t="inlineStr">
+      <c r="AB1" s="14" t="inlineStr">
         <is>
           <t>SKB Valid Until</t>
-        </is>
-      </c>
-      <c r="O1" s="14" t="inlineStr">
-        <is>
-          <t>Hold Commission</t>
-        </is>
-      </c>
-      <c r="P1" s="14" t="inlineStr">
-        <is>
-          <t>Note Perubahan</t>
         </is>
       </c>
     </row>
@@ -1335,67 +1407,131 @@
       <c r="A2" s="15" t="n">
         <v>2265</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="15" t="n">
+        <v>2265</v>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>Mitra JKT @ Pejuang</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Mitra JKT @ Pejuang</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Andi</t>
         </is>
       </c>
-      <c r="D2" s="15" t="n">
-        <v>12345</v>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>ANDI</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>All Region - Non POH</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>mitra@example.com</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>3201234506850001</t>
+        </is>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>01.234.567.8-901.000</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>0123456789012345</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>Pribadi</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
-        <is>
-          <t>mitra@example.com</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>Jl. Contoh No.1, Bekasi</t>
+        </is>
+      </c>
+      <c r="O2" s="15" t="inlineStr">
+        <is>
+          <t>Jl. Contoh No.1, Bekasi</t>
+        </is>
+      </c>
+      <c r="P2" s="15" t="inlineStr">
         <is>
           <t>Jl. Contoh No.1</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="Q2" s="15" t="inlineStr">
         <is>
           <t>Bekasi</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>BCA</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="S2" s="15" t="inlineStr">
         <is>
           <t>Andi</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>1234567890</t>
         </is>
       </c>
-      <c r="M2" s="15" t="n"/>
-      <c r="N2" s="15" t="n"/>
-      <c r="O2" s="15" t="inlineStr">
+      <c r="U2" s="15" t="inlineStr">
+        <is>
+          <t>CUS012345 ANDI</t>
+        </is>
+      </c>
+      <c r="V2" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" s="15" t="n"/>
+      <c r="W2" s="15" t="inlineStr">
+        <is>
+          <t>New mitra onboarded Jul-2026</t>
+        </is>
+      </c>
+      <c r="X2" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y2" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z2" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA2" s="15" t="inlineStr"/>
+      <c r="AB2" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
